--- a/games-logger.xlsx
+++ b/games-logger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unilever/Desktop/Active-Projects/ai-agents/walking-football/video-processing/walking-football-video-processing-application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D82D18-DC36-444C-A0E8-6517559AF61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30B6428-C067-DB40-BD64-AD66C308EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-61800" yWindow="3940" windowWidth="59220" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60400" yWindow="6480" windowWidth="59220" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="games" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="248">
   <si>
     <t>game_id</t>
   </si>
@@ -966,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -979,6 +979,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2635,14 +2636,8 @@
       <c r="V24" t="s">
         <v>108</v>
       </c>
-      <c r="W24" t="s">
-        <v>142</v>
-      </c>
-      <c r="X24" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>142</v>
+      <c r="Y24" s="10">
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="AA24">
         <v>15</v>

--- a/games-logger.xlsx
+++ b/games-logger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unilever/Desktop/Active-Projects/ai-agents/walking-football/video-processing/walking-football-video-processing-application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30B6428-C067-DB40-BD64-AD66C308EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ACF09E-A59C-C440-8CCC-395C92DE712C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60400" yWindow="6480" windowWidth="59220" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
         <v>108</v>
       </c>
       <c r="Y24" s="10">
-        <v>6.9444444444444441E-3</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="AA24">
         <v>15</v>
